--- a/docs/d/50/inyear.xlsx
+++ b/docs/d/50/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 58 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 56 clubs short</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1742,8 +1742,8 @@
       <c r="Y10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z10" s="9" t="n">
-        <v>0</v>
+      <c r="Z10" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA10" s="10" t="n">
         <v>1</v>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>10</v>
@@ -2646,8 +2646,8 @@
       <c r="R19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S19" s="9" t="n">
-        <v>1</v>
+      <c r="S19" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T19" s="10" t="n">
         <v>1</v>
@@ -5554,7 +5554,7 @@
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>10</v>
@@ -5597,8 +5597,8 @@
       <c r="P48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" s="9" t="n">
-        <v>1</v>
+      <c r="Q48" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R48" s="9" t="n">
         <v>0</v>
@@ -14494,7 +14494,7 @@
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -14564,8 +14564,8 @@
       <c r="Y136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z136" s="9" t="n">
-        <v>0</v>
+      <c r="Z136" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA136" s="10" t="n">
         <v>1</v>
@@ -15654,7 +15654,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -15687,7 +15687,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -15918,7 +15918,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -16545,7 +16545,7 @@
         <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>

--- a/docs/d/50/inyear.xlsx
+++ b/docs/d/50/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:40 PDT.</t>
         </is>
       </c>
     </row>
@@ -2268,7 +2268,11 @@
       <c r="AB15" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC15" s="4" t="inlineStr"/>
+      <c r="AC15" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -2474,7 +2478,11 @@
       <c r="AB17" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC17" s="4" t="inlineStr"/>
+      <c r="AC17" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -2781,7 +2789,11 @@
       <c r="AB20" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC20" s="4" t="inlineStr"/>
+      <c r="AC20" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -3189,7 +3201,11 @@
       <c r="AB24" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC24" s="4" t="inlineStr"/>
+      <c r="AC24" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -4304,7 +4320,11 @@
       <c r="AB35" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC35" s="4" t="inlineStr"/>
+      <c r="AC35" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -4716,7 +4736,11 @@
       <c r="AB39" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC39" s="4" t="inlineStr"/>
+      <c r="AC39" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -5330,7 +5354,11 @@
       <c r="AB45" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC45" s="4" t="inlineStr"/>
+      <c r="AC45" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -9960,7 +9988,11 @@
       <c r="AB91" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC91" s="4" t="inlineStr"/>
+      <c r="AC91" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
@@ -10986,7 +11018,11 @@
       <c r="AB101" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC101" s="4" t="inlineStr"/>
+      <c r="AC101" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
@@ -12012,7 +12048,11 @@
       <c r="AB111" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC111" s="4" t="inlineStr"/>
+      <c r="AC111" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
@@ -13555,7 +13595,11 @@
       <c r="AB126" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC126" s="4" t="inlineStr"/>
+      <c r="AC126" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
@@ -13656,7 +13700,11 @@
       <c r="AB127" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC127" s="4" t="inlineStr"/>
+      <c r="AC127" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
@@ -14371,7 +14419,11 @@
       <c r="AB134" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC134" s="4" t="inlineStr"/>
+      <c r="AC134" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
@@ -14472,7 +14524,11 @@
       <c r="AB135" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC135" s="4" t="inlineStr"/>
+      <c r="AC135" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
@@ -14985,7 +15041,11 @@
       <c r="AB140" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC140" s="4" t="inlineStr"/>
+      <c r="AC140" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
@@ -15292,7 +15352,11 @@
       <c r="AB143" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC143" s="4" t="inlineStr"/>
+      <c r="AC143" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="4" t="inlineStr">

--- a/docs/d/50/inyear.xlsx
+++ b/docs/d/50/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 8 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 8 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 56 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 51 clubs short</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>10</v>
@@ -1843,8 +1843,8 @@
       <c r="Y11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z11" s="9" t="n">
-        <v>0</v>
+      <c r="Z11" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA11" s="10" t="n">
         <v>1</v>
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>10</v>
@@ -2203,13 +2203,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>4</v>
       </c>
       <c r="W15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X15" s="10" t="n">
         <v>7</v>
@@ -2259,8 +2259,8 @@
       <c r="Y15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z15" s="9" t="n">
-        <v>0</v>
+      <c r="Z15" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA15" s="10" t="n">
         <v>1</v>
@@ -4556,7 +4556,7 @@
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F38" s="6" t="n">
         <v>10</v>
@@ -4626,8 +4626,8 @@
       <c r="Y38" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z38" s="9" t="n">
-        <v>0</v>
+      <c r="Z38" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA38" s="10" t="n">
         <v>1</v>
@@ -4671,13 +4671,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>4</v>
       </c>
       <c r="W39" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X39" s="10" t="n">
         <v>7</v>
@@ -5990,7 +5990,7 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>10</v>
@@ -6060,8 +6060,8 @@
       <c r="Y52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z52" s="9" t="n">
-        <v>0</v>
+      <c r="Z52" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA52" s="10" t="n">
         <v>1</v>
@@ -7707,7 +7707,7 @@
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F69" s="6" t="n">
         <v>10</v>
@@ -7721,17 +7721,17 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L69" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>6</v>
+      </c>
+      <c r="L69" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M69" s="8" t="n">
@@ -7765,11 +7765,11 @@
       <c r="U69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V69" s="9" t="n">
-        <v>1</v>
+      <c r="V69" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W69" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X69" s="9" t="n">
         <v>0</v>
@@ -7777,8 +7777,8 @@
       <c r="Y69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z69" s="9" t="n">
-        <v>0</v>
+      <c r="Z69" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA69" s="10" t="n">
         <v>1</v>
@@ -11983,13 +11983,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
@@ -12031,7 +12031,7 @@
         <v>4</v>
       </c>
       <c r="W111" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X111" s="10" t="n">
         <v>7</v>
@@ -15718,7 +15718,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -15751,7 +15751,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -15883,7 +15883,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -15982,7 +15982,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -16147,7 +16147,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -16162,7 +16162,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">

--- a/docs/d/50/inyear.xlsx
+++ b/docs/d/50/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 8 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 8 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 51 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 32 clubs short</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>10</v>
@@ -1023,8 +1023,8 @@
       <c r="Y3" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z3" s="9" t="n">
-        <v>0</v>
+      <c r="Z3" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA3" s="10" t="n">
         <v>1</v>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>10</v>
@@ -1330,8 +1330,8 @@
       <c r="Y6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z6" s="9" t="n">
-        <v>0</v>
+      <c r="Z6" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA6" s="10" t="n">
         <v>1</v>
@@ -1878,7 +1878,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>10</v>
@@ -1892,17 +1892,17 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>7</v>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M12" s="8" t="n">
@@ -1936,11 +1936,11 @@
       <c r="U12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V12" s="9" t="n">
-        <v>0</v>
+      <c r="V12" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W12" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X12" s="9" t="n">
         <v>3</v>
@@ -1948,8 +1948,8 @@
       <c r="Y12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z12" s="9" t="n">
-        <v>0</v>
+      <c r="Z12" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA12" s="10" t="n">
         <v>1</v>
@@ -1979,7 +1979,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -2049,8 +2049,8 @@
       <c r="Y13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z13" s="9" t="n">
-        <v>0</v>
+      <c r="Z13" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA13" s="10" t="n">
         <v>1</v>
@@ -2134,7 +2134,7 @@
         <v>0</v>
       </c>
       <c r="S14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T14" s="9" t="n">
         <v>0</v>
@@ -2880,7 +2880,7 @@
         <v>0</v>
       </c>
       <c r="X21" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y21" s="9" t="n">
         <v>0</v>
@@ -3433,7 +3433,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3503,8 +3503,8 @@
       <c r="Y27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z27" s="9" t="n">
-        <v>0</v>
+      <c r="Z27" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA27" s="10" t="n">
         <v>1</v>
@@ -3635,7 +3635,7 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>10</v>
@@ -3705,8 +3705,8 @@
       <c r="Y29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z29" s="9" t="n">
-        <v>0</v>
+      <c r="Z29" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA29" s="10" t="n">
         <v>1</v>
@@ -3837,7 +3837,7 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>10</v>
@@ -3907,8 +3907,8 @@
       <c r="Y31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z31" s="9" t="n">
-        <v>0</v>
+      <c r="Z31" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA31" s="10" t="n">
         <v>1</v>
@@ -4451,7 +4451,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4494,14 +4494,14 @@
       <c r="P37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" s="9" t="n">
-        <v>1</v>
+      <c r="Q37" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S37" s="9" t="n">
-        <v>1</v>
+      <c r="S37" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T37" s="10" t="n">
         <v>1</v>
@@ -5174,7 +5174,7 @@
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>10</v>
@@ -5244,8 +5244,8 @@
       <c r="Y44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z44" s="9" t="n">
-        <v>0</v>
+      <c r="Z44" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA44" s="10" t="n">
         <v>1</v>
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>10</v>
@@ -5450,8 +5450,8 @@
       <c r="Y46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z46" s="9" t="n">
-        <v>0</v>
+      <c r="Z46" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA46" s="10" t="n">
         <v>1</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="P50" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q50" s="9" t="n">
         <v>0</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="P54" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q54" s="9" t="n">
         <v>1</v>
@@ -6416,13 +6416,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
@@ -6458,10 +6458,10 @@
         <v>1</v>
       </c>
       <c r="U56" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V56" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W56" s="9" t="n">
         <v>0</v>
@@ -7806,7 +7806,7 @@
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>10</v>
@@ -7858,8 +7858,8 @@
       <c r="S70" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T70" s="9" t="n">
-        <v>0</v>
+      <c r="T70" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U70" s="9" t="n">
         <v>0</v>
@@ -8004,7 +8004,7 @@
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>10</v>
@@ -8074,8 +8074,8 @@
       <c r="Y72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z72" s="9" t="n">
-        <v>0</v>
+      <c r="Z72" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA72" s="10" t="n">
         <v>1</v>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F75" s="6" t="n">
         <v>10</v>
@@ -8371,8 +8371,8 @@
       <c r="Y75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z75" s="9" t="n">
-        <v>0</v>
+      <c r="Z75" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA75" s="10" t="n">
         <v>1</v>
@@ -8994,7 +8994,7 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -9064,8 +9064,8 @@
       <c r="Y82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z82" s="9" t="n">
-        <v>0</v>
+      <c r="Z82" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA82" s="10" t="n">
         <v>1</v>
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>10</v>
@@ -9773,8 +9773,8 @@
       <c r="Y89" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z89" s="9" t="n">
-        <v>0</v>
+      <c r="Z89" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA89" s="10" t="n">
         <v>1</v>
@@ -10834,7 +10834,7 @@
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10904,8 +10904,8 @@
       <c r="Y100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z100" s="9" t="n">
-        <v>0</v>
+      <c r="Z100" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA100" s="10" t="n">
         <v>1</v>
@@ -11210,7 +11210,7 @@
         <v>0</v>
       </c>
       <c r="X103" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y103" s="9" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -12144,8 +12144,8 @@
       <c r="Y112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z112" s="9" t="n">
-        <v>0</v>
+      <c r="Z112" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA112" s="10" t="n">
         <v>1</v>
@@ -13100,7 +13100,7 @@
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -13170,8 +13170,8 @@
       <c r="Y122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z122" s="9" t="n">
-        <v>0</v>
+      <c r="Z122" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA122" s="10" t="n">
         <v>1</v>
@@ -13827,7 +13827,7 @@
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>10</v>
@@ -13897,8 +13897,8 @@
       <c r="Y129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z129" s="9" t="n">
-        <v>0</v>
+      <c r="Z129" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA129" s="10" t="n">
         <v>1</v>
@@ -13969,7 +13969,7 @@
         </is>
       </c>
       <c r="P130" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q130" s="9" t="n">
         <v>0</v>
@@ -14239,7 +14239,7 @@
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -14291,8 +14291,8 @@
       <c r="S133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T133" s="9" t="n">
-        <v>0</v>
+      <c r="T133" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U133" s="9" t="n">
         <v>0</v>
@@ -14756,7 +14756,7 @@
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>10</v>
@@ -14826,8 +14826,8 @@
       <c r="Y138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z138" s="9" t="n">
-        <v>0</v>
+      <c r="Z138" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA138" s="10" t="n">
         <v>1</v>
@@ -15067,7 +15067,7 @@
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F141" s="6" t="n">
         <v>10</v>
@@ -15137,8 +15137,8 @@
       <c r="Y141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z141" s="9" t="n">
-        <v>0</v>
+      <c r="Z141" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA141" s="10" t="n">
         <v>1</v>
@@ -15493,13 +15493,13 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J145" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L145" s="4" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>0</v>
       </c>
       <c r="V145" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W145" s="9" t="n">
         <v>0</v>
@@ -15652,7 +15652,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -15685,7 +15685,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -15718,7 +15718,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -15733,7 +15733,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -15817,7 +15817,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -15850,7 +15850,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -15883,13 +15883,13 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -15949,7 +15949,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -16147,7 +16147,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -16180,7 +16180,7 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -16213,7 +16213,7 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -16279,7 +16279,7 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -16345,7 +16345,7 @@
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -16444,7 +16444,7 @@
         <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -16510,7 +16510,7 @@
         <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -16576,7 +16576,7 @@
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -16609,7 +16609,7 @@
         <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -16642,7 +16642,7 @@
         <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -16675,7 +16675,7 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>

--- a/docs/d/50/inyear.xlsx
+++ b/docs/d/50/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 8 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 8 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 32 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 32 clubs short</t>
         </is>
       </c>
     </row>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -967,13 +967,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
@@ -1068,13 +1068,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>0</v>
       </c>
       <c r="V4" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W4" s="9" t="n">
         <v>0</v>
@@ -1173,13 +1173,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>10</v>
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
@@ -1312,8 +1312,8 @@
       <c r="S6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T6" s="9" t="n">
-        <v>0</v>
+      <c r="T6" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U6" s="9" t="n">
         <v>0</v>
@@ -1375,13 +1375,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
@@ -1480,13 +1480,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
@@ -1585,13 +1585,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
@@ -1686,13 +1686,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>0</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W10" s="9" t="n">
         <v>0</v>
@@ -1832,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="V11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W11" s="9" t="n">
         <v>0</v>
@@ -1892,17 +1892,17 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>2</v>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M12" s="8" t="n">
@@ -1993,13 +1993,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
@@ -2098,13 +2098,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
@@ -2203,17 +2203,17 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-15</v>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M15" s="8" t="n">
@@ -2308,13 +2308,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
@@ -2413,13 +2413,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>4</v>
+        <v>-17</v>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
@@ -2518,13 +2518,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>10</v>
@@ -2619,17 +2619,17 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M19" s="8" t="n">
@@ -2660,8 +2660,8 @@
       <c r="T19" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U19" s="9" t="n">
-        <v>0</v>
+      <c r="U19" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V19" s="9" t="n">
         <v>1</v>
@@ -2724,13 +2724,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>0</v>
       </c>
       <c r="V20" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W20" s="9" t="n">
         <v>0</v>
@@ -2829,13 +2829,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>0</v>
       </c>
       <c r="V21" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W21" s="9" t="n">
         <v>0</v>
@@ -2930,13 +2930,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
@@ -3035,13 +3035,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>0</v>
       </c>
       <c r="V23" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W23" s="9" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>10</v>
@@ -3136,13 +3136,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         </is>
       </c>
       <c r="P24" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q24" s="9" t="n">
         <v>0</v>
@@ -3171,8 +3171,8 @@
       <c r="R24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S24" s="9" t="n">
-        <v>1</v>
+      <c r="S24" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T24" s="9" t="n">
         <v>0</v>
@@ -3241,13 +3241,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>0</v>
       </c>
       <c r="V25" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W25" s="9" t="n">
         <v>0</v>
@@ -3342,17 +3342,17 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L26" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M26" s="8" t="n">
@@ -3447,13 +3447,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
@@ -3548,13 +3548,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
@@ -3649,13 +3649,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
@@ -3851,13 +3851,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
@@ -4053,13 +4053,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
@@ -4154,13 +4154,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
@@ -4255,13 +4255,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         <v>4</v>
       </c>
       <c r="W35" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X35" s="10" t="n">
         <v>7</v>
@@ -4346,7 +4346,7 @@
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F36" s="6" t="n">
         <v>10</v>
@@ -4360,13 +4360,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
@@ -4407,8 +4407,8 @@
       <c r="V36" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W36" s="9" t="n">
-        <v>2</v>
+      <c r="W36" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X36" s="10" t="n">
         <v>5</v>
@@ -4465,13 +4465,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -4570,13 +4570,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>0</v>
       </c>
       <c r="V38" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W38" s="9" t="n">
         <v>0</v>
@@ -4671,13 +4671,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>6</v>
+        <v>-6</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         </is>
       </c>
       <c r="P39" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q39" s="9" t="n">
         <v>1</v>
@@ -4719,7 +4719,7 @@
         <v>4</v>
       </c>
       <c r="W39" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X39" s="10" t="n">
         <v>7</v>
@@ -4776,13 +4776,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
@@ -4877,13 +4877,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -4982,13 +4982,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
@@ -5026,8 +5026,8 @@
       <c r="U42" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V42" s="9" t="n">
-        <v>2</v>
+      <c r="V42" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W42" s="9" t="n">
         <v>0</v>
@@ -5087,13 +5087,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
@@ -5188,13 +5188,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>0</v>
       </c>
       <c r="V44" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W44" s="9" t="n">
         <v>0</v>
@@ -5289,13 +5289,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>45</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>3</v>
+        <v>-17</v>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>10</v>
@@ -5394,13 +5394,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>47</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>3</v>
+        <v>-12</v>
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
@@ -5438,8 +5438,8 @@
       <c r="U46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V46" s="9" t="n">
-        <v>3</v>
+      <c r="V46" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W46" s="9" t="n">
         <v>0</v>
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
@@ -5596,13 +5596,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         </is>
       </c>
       <c r="P48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q48" s="10" t="n">
         <v>2</v>
@@ -5632,7 +5632,7 @@
         <v>0</v>
       </c>
       <c r="S48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T48" s="10" t="n">
         <v>1</v>
@@ -5641,7 +5641,7 @@
         <v>0</v>
       </c>
       <c r="V48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W48" s="9" t="n">
         <v>0</v>
@@ -5701,13 +5701,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
@@ -5802,13 +5802,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -6004,17 +6004,17 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L52" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L52" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M52" s="8" t="n">
@@ -6105,13 +6105,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
@@ -6192,7 +6192,7 @@
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F54" s="6" t="n">
         <v>10</v>
@@ -6206,17 +6206,17 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L54" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M54" s="8" t="n">
@@ -6244,8 +6244,8 @@
       <c r="S54" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T54" s="9" t="n">
-        <v>0</v>
+      <c r="T54" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U54" s="9" t="n">
         <v>0</v>
@@ -6311,13 +6311,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>10</v>
@@ -6416,17 +6416,17 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L56" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L56" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M56" s="8" t="n">
@@ -6460,8 +6460,8 @@
       <c r="U56" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="V56" s="9" t="n">
-        <v>2</v>
+      <c r="V56" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W56" s="9" t="n">
         <v>0</v>
@@ -6521,13 +6521,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>48</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>4</v>
+        <v>-8</v>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
         <v>4</v>
       </c>
       <c r="W57" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X57" s="10" t="n">
         <v>6</v>
@@ -6626,13 +6626,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>46</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>4</v>
       </c>
       <c r="W58" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X58" s="9" t="n">
         <v>0</v>
@@ -6727,17 +6727,17 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-24</v>
+      </c>
+      <c r="L59" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M59" s="8" t="n">
@@ -6828,13 +6828,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
@@ -6929,13 +6929,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         </is>
       </c>
       <c r="P61" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q61" s="9" t="n">
         <v>1</v>
@@ -6977,7 +6977,7 @@
         <v>4</v>
       </c>
       <c r="W61" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X61" s="10" t="n">
         <v>7</v>
@@ -7028,17 +7028,17 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L62" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L62" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M62" s="8" t="n">
@@ -7226,13 +7226,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
@@ -7325,13 +7325,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
@@ -7424,17 +7424,17 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L66" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M66" s="8" t="n">
@@ -7509,7 +7509,7 @@
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>10</v>
@@ -7523,13 +7523,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
@@ -7567,8 +7567,8 @@
       <c r="U67" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V67" s="9" t="n">
-        <v>3</v>
+      <c r="V67" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W67" s="9" t="n">
         <v>0</v>
@@ -7721,17 +7721,17 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L69" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>4</v>
+      </c>
+      <c r="L69" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M69" s="8" t="n">
@@ -7806,7 +7806,7 @@
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>10</v>
@@ -7820,13 +7820,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
@@ -7864,8 +7864,8 @@
       <c r="U70" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V70" s="9" t="n">
-        <v>3</v>
+      <c r="V70" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W70" s="9" t="n">
         <v>0</v>
@@ -7919,13 +7919,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
@@ -8018,13 +8018,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
@@ -8117,13 +8117,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
@@ -8216,13 +8216,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
@@ -8315,13 +8315,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8414,13 +8414,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
@@ -8458,11 +8458,11 @@
       <c r="U76" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V76" s="9" t="n">
-        <v>2</v>
+      <c r="V76" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W76" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X76" s="10" t="n">
         <v>5</v>
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
@@ -8612,13 +8612,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8697,7 +8697,7 @@
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>10</v>
@@ -8711,13 +8711,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
@@ -8755,8 +8755,8 @@
       <c r="U79" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V79" s="9" t="n">
-        <v>3</v>
+      <c r="V79" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W79" s="9" t="n">
         <v>0</v>
@@ -8810,13 +8810,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
@@ -8909,13 +8909,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
@@ -9053,7 +9053,7 @@
         <v>0</v>
       </c>
       <c r="V82" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W82" s="9" t="n">
         <v>0</v>
@@ -9107,17 +9107,17 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>56</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-49</v>
+      </c>
+      <c r="L83" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M83" s="8" t="n">
@@ -9208,13 +9208,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L84" s="7" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>1</v>
       </c>
       <c r="V84" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W84" s="9" t="n">
         <v>0</v>
@@ -9309,13 +9309,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
@@ -9414,13 +9414,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L86" s="7" t="inlineStr">
         <is>
@@ -9515,13 +9515,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
@@ -9616,13 +9616,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L88" s="7" t="inlineStr">
         <is>
@@ -9717,13 +9717,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L90" s="7" t="inlineStr">
         <is>
@@ -9923,13 +9923,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>3</v>
+        <v>-6</v>
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
@@ -10028,17 +10028,17 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L92" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L92" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M92" s="8" t="n">
@@ -10133,13 +10133,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
@@ -10436,13 +10436,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -10523,7 +10523,7 @@
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10537,13 +10537,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
@@ -10581,11 +10581,11 @@
       <c r="U97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V97" s="9" t="n">
-        <v>2</v>
+      <c r="V97" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W97" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X97" s="10" t="n">
         <v>7</v>
@@ -10642,13 +10642,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
@@ -10747,13 +10747,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
         <v>4</v>
       </c>
       <c r="W99" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X99" s="10" t="n">
         <v>6</v>
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L100" s="7" t="inlineStr">
         <is>
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -10953,17 +10953,17 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L101" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L101" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M101" s="8" t="n">
@@ -10997,8 +10997,8 @@
       <c r="U101" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V101" s="9" t="n">
-        <v>2</v>
+      <c r="V101" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W101" s="9" t="n">
         <v>0</v>
@@ -11058,17 +11058,17 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L102" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M102" s="8" t="n">
@@ -11103,7 +11103,7 @@
         <v>0</v>
       </c>
       <c r="V102" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W102" s="9" t="n">
         <v>0</v>
@@ -11159,13 +11159,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
@@ -11264,17 +11264,17 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L104" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L104" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M104" s="8" t="n">
@@ -11676,13 +11676,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L108" s="7" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
         <v>0</v>
       </c>
       <c r="V108" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W108" s="9" t="n">
         <v>0</v>
@@ -11777,17 +11777,17 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L109" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L109" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M109" s="8" t="n">
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L110" s="7" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>0</v>
       </c>
       <c r="V110" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W110" s="9" t="n">
         <v>0</v>
@@ -11983,13 +11983,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
@@ -12088,13 +12088,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L112" s="7" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         <v>0</v>
       </c>
       <c r="V112" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W112" s="9" t="n">
         <v>0</v>
@@ -12216,7 +12216,7 @@
         </is>
       </c>
       <c r="P113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q113" s="9" t="n">
         <v>0</v>
@@ -12234,7 +12234,7 @@
         <v>0</v>
       </c>
       <c r="V113" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W113" s="9" t="n">
         <v>0</v>
@@ -12290,13 +12290,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
@@ -12395,17 +12395,17 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L115" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L115" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M115" s="8" t="n">
@@ -12500,13 +12500,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L116" s="7" t="inlineStr">
         <is>
@@ -12601,13 +12601,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>1</v>
+        <v>-11</v>
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
@@ -12702,13 +12702,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L118" s="7" t="inlineStr">
         <is>
@@ -12803,17 +12803,17 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L119" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L119" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M119" s="8" t="n">
@@ -12833,7 +12833,7 @@
         <v>1</v>
       </c>
       <c r="Q119" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R119" s="9" t="n">
         <v>0</v>
@@ -12908,13 +12908,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L120" s="7" t="inlineStr">
         <is>
@@ -13013,13 +13013,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>3</v>
+        <v>-8</v>
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
@@ -13114,17 +13114,17 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L122" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L122" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M122" s="8" t="n">
@@ -13205,7 +13205,7 @@
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>10</v>
@@ -13219,13 +13219,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>3</v>
+        <v>-9</v>
       </c>
       <c r="L123" s="4" t="inlineStr">
         <is>
@@ -13263,8 +13263,8 @@
       <c r="U123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V123" s="9" t="n">
-        <v>3</v>
+      <c r="V123" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W123" s="9" t="n">
         <v>0</v>
@@ -13324,17 +13324,17 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L124" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L124" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M124" s="8" t="n">
@@ -13516,7 +13516,7 @@
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>10</v>
@@ -13530,13 +13530,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
@@ -13571,8 +13571,8 @@
       <c r="T126" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U126" s="9" t="n">
-        <v>0</v>
+      <c r="U126" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V126" s="9" t="n">
         <v>2</v>
@@ -13635,17 +13635,17 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L127" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L127" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M127" s="8" t="n">
@@ -13680,7 +13680,7 @@
         <v>0</v>
       </c>
       <c r="V127" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W127" s="9" t="n">
         <v>0</v>
@@ -13740,13 +13740,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L128" s="7" t="inlineStr">
         <is>
@@ -13827,7 +13827,7 @@
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>10</v>
@@ -13841,13 +13841,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L129" s="4" t="inlineStr">
         <is>
@@ -13885,8 +13885,8 @@
       <c r="U129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V129" s="9" t="n">
-        <v>0</v>
+      <c r="V129" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W129" s="9" t="n">
         <v>0</v>
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F130" s="6" t="n">
         <v>10</v>
@@ -13942,13 +13942,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L130" s="4" t="inlineStr">
         <is>
@@ -13986,11 +13986,11 @@
       <c r="U130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V130" s="9" t="n">
+      <c r="V130" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W130" s="9" t="n">
         <v>3</v>
-      </c>
-      <c r="W130" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="X130" s="10" t="n">
         <v>4</v>
@@ -14047,13 +14047,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="L131" s="7" t="inlineStr">
         <is>
@@ -14148,13 +14148,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L132" s="7" t="inlineStr">
         <is>
@@ -14175,7 +14175,7 @@
         </is>
       </c>
       <c r="P132" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q132" s="9" t="n">
         <v>0</v>
@@ -14253,13 +14253,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L133" s="7" t="inlineStr">
         <is>
@@ -14354,17 +14354,17 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L134" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L134" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M134" s="8" t="n">
@@ -14564,17 +14564,17 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L136" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L136" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M136" s="8" t="n">
@@ -14665,17 +14665,17 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L137" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L137" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M137" s="8" t="n">
@@ -14770,13 +14770,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L138" s="7" t="inlineStr">
         <is>
@@ -14871,13 +14871,13 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L139" s="7" t="inlineStr">
         <is>
@@ -14976,13 +14976,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L140" s="4" t="inlineStr">
         <is>
@@ -15021,7 +15021,7 @@
         <v>1</v>
       </c>
       <c r="V140" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W140" s="9" t="n">
         <v>0</v>
@@ -15081,13 +15081,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L141" s="7" t="inlineStr">
         <is>
@@ -15186,13 +15186,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L142" s="7" t="inlineStr">
         <is>
@@ -15287,13 +15287,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L143" s="4" t="inlineStr">
         <is>
@@ -15392,13 +15392,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
@@ -15440,7 +15440,7 @@
         <v>4</v>
       </c>
       <c r="W144" s="10" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="X144" s="10" t="n">
         <v>4</v>
@@ -15685,7 +15685,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -15733,7 +15733,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -15751,13 +15751,13 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -15766,7 +15766,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -15817,7 +15817,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -15832,7 +15832,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -15883,7 +15883,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -15916,7 +15916,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -15949,7 +15949,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -15997,7 +15997,7 @@
         <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -16015,7 +16015,7 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -16030,7 +16030,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -16063,7 +16063,7 @@
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -16096,7 +16096,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -16114,7 +16114,7 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -16129,7 +16129,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -16147,7 +16147,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -16162,7 +16162,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -16180,7 +16180,7 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -16213,7 +16213,7 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -16261,7 +16261,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -16312,7 +16312,7 @@
         <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -16327,7 +16327,7 @@
         <v>2</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -16345,7 +16345,7 @@
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -16360,7 +16360,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -16393,7 +16393,7 @@
         <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -16426,7 +16426,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -16459,7 +16459,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -16492,7 +16492,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -16510,7 +16510,7 @@
         <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -16525,7 +16525,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -16543,7 +16543,7 @@
         <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -16558,7 +16558,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -16576,7 +16576,7 @@
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -16624,7 +16624,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -16657,7 +16657,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">

--- a/docs/d/50/inyear.xlsx
+++ b/docs/d/50/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/50/inyear.xlsx
+++ b/docs/d/50/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/50/inyear.xlsx
+++ b/docs/d/50/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/50/inyear.xlsx
+++ b/docs/d/50/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/50/inyear.xlsx
+++ b/docs/d/50/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 8 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 8 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 32 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 32 clubs short</t>
         </is>
       </c>
     </row>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -1585,13 +1585,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
@@ -2203,13 +2203,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>4</v>
       </c>
       <c r="W15" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X15" s="10" t="n">
         <v>7</v>
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="S19" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T19" s="10" t="n">
         <v>1</v>
@@ -3241,13 +3241,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
@@ -3447,13 +3447,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         <v>0</v>
       </c>
       <c r="V27" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W27" s="9" t="n">
         <v>0</v>
@@ -4360,17 +4360,17 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L36" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>4</v>
+      </c>
+      <c r="L36" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M36" s="8" t="n">
@@ -4982,13 +4982,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>4</v>
       </c>
       <c r="W42" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X42" s="10" t="n">
         <v>6</v>
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>10</v>
@@ -5289,13 +5289,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>45</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>-17</v>
+        <v>-13</v>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
@@ -5333,11 +5333,11 @@
       <c r="U45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V45" s="9" t="n">
-        <v>3</v>
+      <c r="V45" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W45" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X45" s="10" t="n">
         <v>7</v>
@@ -6004,13 +6004,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>-13</v>
+        <v>-11</v>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
@@ -6727,13 +6727,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>-24</v>
+        <v>-7</v>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>10</v>
@@ -6956,10 +6956,10 @@
         </is>
       </c>
       <c r="P61" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q61" s="10" t="n">
         <v>2</v>
-      </c>
-      <c r="Q61" s="9" t="n">
-        <v>1</v>
       </c>
       <c r="R61" s="9" t="n">
         <v>0</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -7363,8 +7363,8 @@
       <c r="S65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T65" s="9" t="n">
-        <v>0</v>
+      <c r="T65" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U65" s="9" t="n">
         <v>0</v>
@@ -7550,7 +7550,7 @@
         </is>
       </c>
       <c r="P67" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q67" s="9" t="n">
         <v>0</v>
@@ -7559,7 +7559,7 @@
         <v>0</v>
       </c>
       <c r="S67" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T67" s="9" t="n">
         <v>0</v>
@@ -8612,13 +8612,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         </is>
       </c>
       <c r="P79" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q79" s="9" t="n">
         <v>1</v>
@@ -9909,7 +9909,7 @@
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>10</v>
@@ -9952,8 +9952,8 @@
       <c r="P91" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q91" s="9" t="n">
-        <v>1</v>
+      <c r="Q91" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R91" s="9" t="n">
         <v>0</v>
@@ -10523,7 +10523,7 @@
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10537,13 +10537,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         </is>
       </c>
       <c r="P97" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q97" s="9" t="n">
         <v>0</v>
@@ -10584,8 +10584,8 @@
       <c r="V97" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W97" s="9" t="n">
-        <v>3</v>
+      <c r="W97" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X97" s="10" t="n">
         <v>7</v>
@@ -12088,13 +12088,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L112" s="7" t="inlineStr">
         <is>
@@ -12290,13 +12290,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
@@ -12338,7 +12338,7 @@
         <v>4</v>
       </c>
       <c r="W114" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X114" s="10" t="n">
         <v>6</v>
@@ -12395,13 +12395,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
@@ -12601,13 +12601,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>-11</v>
+        <v>-9</v>
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
@@ -12646,7 +12646,7 @@
         <v>0</v>
       </c>
       <c r="V117" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W117" s="9" t="n">
         <v>0</v>
@@ -12908,13 +12908,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L120" s="7" t="inlineStr">
         <is>
@@ -13013,13 +13013,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
@@ -13219,13 +13219,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L123" s="4" t="inlineStr">
         <is>
@@ -14047,13 +14047,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L131" s="7" t="inlineStr">
         <is>
@@ -14148,13 +14148,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L132" s="7" t="inlineStr">
         <is>
@@ -14193,7 +14193,7 @@
         <v>0</v>
       </c>
       <c r="V132" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W132" s="9" t="n">
         <v>0</v>
@@ -14340,7 +14340,7 @@
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F134" s="6" t="n">
         <v>10</v>
@@ -14354,17 +14354,17 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>-7</v>
-      </c>
-      <c r="L134" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-2</v>
+      </c>
+      <c r="L134" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M134" s="8" t="n">
@@ -14398,11 +14398,11 @@
       <c r="U134" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V134" s="9" t="n">
-        <v>3</v>
+      <c r="V134" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W134" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X134" s="10" t="n">
         <v>7</v>
@@ -14665,13 +14665,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L137" s="7" t="inlineStr">
         <is>
@@ -15186,13 +15186,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L142" s="7" t="inlineStr">
         <is>
@@ -15392,13 +15392,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
@@ -15440,7 +15440,7 @@
         <v>4</v>
       </c>
       <c r="W144" s="10" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="X144" s="10" t="n">
         <v>4</v>
@@ -15898,7 +15898,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -15949,7 +15949,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -16081,7 +16081,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -16114,7 +16114,7 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -16279,7 +16279,7 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -16312,7 +16312,7 @@
         <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -16609,7 +16609,7 @@
         <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -16624,7 +16624,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">

--- a/docs/d/50/inyear.xlsx
+++ b/docs/d/50/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 8 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 8 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 32 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 32 clubs short</t>
         </is>
       </c>
     </row>
@@ -1585,13 +1585,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>0</v>
       </c>
       <c r="V9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" s="9" t="n">
         <v>0</v>
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>10</v>
@@ -2241,8 +2241,8 @@
       <c r="S15" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T15" s="9" t="n">
-        <v>0</v>
+      <c r="T15" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U15" s="9" t="n">
         <v>0</v>
@@ -2413,13 +2413,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-17</v>
+        <v>-14</v>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         </is>
       </c>
       <c r="P17" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q17" s="9" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>4</v>
       </c>
       <c r="W17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X17" s="10" t="n">
         <v>5</v>
@@ -2518,13 +2518,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
@@ -2655,13 +2655,13 @@
         <v>0</v>
       </c>
       <c r="S19" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T19" s="10" t="n">
         <v>1</v>
       </c>
       <c r="U19" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V19" s="9" t="n">
         <v>1</v>
@@ -2710,7 +2710,7 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>10</v>
@@ -2724,13 +2724,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="P20" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="9" t="n">
         <v>0</v>
@@ -2768,8 +2768,8 @@
       <c r="U20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V20" s="9" t="n">
-        <v>3</v>
+      <c r="V20" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W20" s="9" t="n">
         <v>0</v>
@@ -4360,17 +4360,17 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L36" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M36" s="8" t="n">
@@ -4408,7 +4408,7 @@
         <v>4</v>
       </c>
       <c r="W36" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X36" s="10" t="n">
         <v>5</v>
@@ -5289,13 +5289,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>45</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         <v>4</v>
       </c>
       <c r="W45" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X45" s="10" t="n">
         <v>7</v>
@@ -5623,7 +5623,7 @@
         </is>
       </c>
       <c r="P48" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q48" s="10" t="n">
         <v>2</v>
@@ -5701,13 +5701,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
@@ -6105,13 +6105,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="V53" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W53" s="9" t="n">
         <v>0</v>
@@ -6206,13 +6206,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
@@ -6626,13 +6626,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>46</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>4</v>
       </c>
       <c r="W58" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X58" s="9" t="n">
         <v>0</v>
@@ -7410,7 +7410,7 @@
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>10</v>
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
@@ -7453,8 +7453,8 @@
       <c r="P66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" s="9" t="n">
-        <v>1</v>
+      <c r="Q66" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R66" s="9" t="n">
         <v>0</v>
@@ -7469,7 +7469,7 @@
         <v>0</v>
       </c>
       <c r="V66" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W66" s="9" t="n">
         <v>0</v>
@@ -7721,17 +7721,17 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L69" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L69" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M69" s="8" t="n">
@@ -7820,10 +7820,10 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K70" s="4" t="n">
         <v>-4</v>
@@ -7868,7 +7868,7 @@
         <v>4</v>
       </c>
       <c r="W70" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X70" s="10" t="n">
         <v>7</v>
@@ -8612,13 +8612,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>0</v>
       </c>
       <c r="V78" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W78" s="9" t="n">
         <v>0</v>
@@ -8810,13 +8810,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L100" s="7" t="inlineStr">
         <is>
@@ -10893,7 +10893,7 @@
         <v>0</v>
       </c>
       <c r="V100" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W100" s="9" t="n">
         <v>0</v>
@@ -11250,7 +11250,7 @@
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -11264,13 +11264,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L104" s="7" t="inlineStr">
         <is>
@@ -11308,8 +11308,8 @@
       <c r="U104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V104" s="9" t="n">
-        <v>2</v>
+      <c r="V104" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W104" s="9" t="n">
         <v>0</v>
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L110" s="7" t="inlineStr">
         <is>
@@ -12088,13 +12088,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L112" s="7" t="inlineStr">
         <is>
@@ -12395,13 +12395,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         <v>0</v>
       </c>
       <c r="V115" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W115" s="9" t="n">
         <v>0</v>
@@ -12803,13 +12803,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
@@ -13219,13 +13219,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L123" s="4" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>4</v>
       </c>
       <c r="W123" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X123" s="10" t="n">
         <v>7</v>
@@ -14445,7 +14445,7 @@
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>10</v>
@@ -14500,8 +14500,8 @@
       <c r="T135" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U135" s="9" t="n">
-        <v>0</v>
+      <c r="U135" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V135" s="9" t="n">
         <v>3</v>
@@ -15314,7 +15314,7 @@
         </is>
       </c>
       <c r="P143" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q143" s="9" t="n">
         <v>1</v>
@@ -15392,13 +15392,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
@@ -15440,7 +15440,7 @@
         <v>4</v>
       </c>
       <c r="W144" s="10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X144" s="10" t="n">
         <v>4</v>
@@ -15751,7 +15751,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -15784,7 +15784,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -15898,7 +15898,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -16114,7 +16114,7 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -16162,7 +16162,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -16378,7 +16378,7 @@
         <v>6</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -16609,7 +16609,7 @@
         <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
